--- a/artfynd/A 15687-2023 artfynd.xlsx
+++ b/artfynd/A 15687-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 15687-2023 artfynd.xlsx
+++ b/artfynd/A 15687-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>16796118</v>
+        <v>16796120</v>
       </c>
       <c r="B2" t="n">
-        <v>89170</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3215</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>501760.0484228238</v>
+        <v>501754</v>
       </c>
       <c r="R2" t="n">
-        <v>6607726.504517267</v>
+        <v>6607680</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2014-10-29</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2014-10-29</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,22 +765,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Herbert Kaufmann, Anders Carlberg, Claes Urban Eliasson</t>
+          <t>Herbert Kaufmann, Anders Carlberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>86110078</v>
+        <v>16796085</v>
       </c>
       <c r="B3" t="n">
-        <v>96356</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104628</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219847</v>
+        <v>222412</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -825,27 +805,16 @@
           <t>2</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Östra Öskevik Bäckmanstorp 342,Lindesberg, Vstm</t>
+          <t>Bäckmanstorp, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>501768.1233283121</v>
+        <v>501706</v>
       </c>
       <c r="R3" t="n">
-        <v>6607804.447878768</v>
+        <v>6607823</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -872,22 +841,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2020-06-07</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-10-29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2020-06-07</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-10-29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,15 +861,418 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Herbert Kaufmann</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Herbert Kaufmann</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>16796118</v>
+      </c>
+      <c r="B4" t="n">
+        <v>91680</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Bäckmanstorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>501760</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6607727</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2014-10-29</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2014-10-29</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Herbert Kaufmann</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Herbert Kaufmann, Anders Carlberg, Claes Urban Eliasson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>16796096</v>
+      </c>
+      <c r="B5" t="n">
+        <v>92632</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Bäckmanstorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>501772</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6607842</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2014-10-29</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2014-10-29</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Herbert Kaufmann</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Herbert Kaufmann, Anders Carlberg, Claes Urban Eliasson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>16796117</v>
+      </c>
+      <c r="B6" t="n">
+        <v>92869</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Bäckmanstorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>501763</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6607744</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2014-10-29</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2014-10-29</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Herbert Kaufmann</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Herbert Kaufmann, Anders Carlberg, Claes Urban Eliasson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>86110078</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Östra Öskevik Bäckmanstorp 342,Lindesberg, Vstm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>501768</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6607804</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2020-06-07</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2020-06-07</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
           <t>Lovisa Nilsson</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX7" t="inlineStr">
         <is>
           <t>Lovisa Nilsson</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 15687-2023 artfynd.xlsx
+++ b/artfynd/A 15687-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16796118</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16796096</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16796117</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1075,6 +1095,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86110078</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1172,6 +1197,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16796120</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1273,8 +1303,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16796085</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>